--- a/backend/src/main/resources/mymap/samples/address.xlsx
+++ b/backend/src/main/resources/mymap/samples/address.xlsx
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <cols>
     <col min="1" max="1" width="140.83203125" customWidth="1"/>
   </cols>
@@ -604,42 +604,52 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3. 시도부터 끝까지 정확히 적을수록 잘 찾아집니다. 시도·시군구가 빠진 주소("세종대로 110")는 다른 지역과 섞여 틀리게 찾아질 수 있습니다.</v>
+        <v>3. 시도·시군구까지 적으면 가장 잘 찾아집니다. 시도만 적어도 대부분 찾지만, 같은 도로명·동 이름이 여러 곳에 있으면 한 곳으로 정하지 못해 실패합니다.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4. 건물 이름, 층·호수, 괄호는 빼 주세요. 예) "세종대로 110 시청 본관 3층" → "세종대로 110"</v>
+        <v xml:space="preserve">   이때 결과 보고서에 후보가 나오니 시도·시군구를 붙여 다시 올려 주세요. 시도·시군구가 모두 없는 주소("세종대로 110")는 대개 이렇게 실패합니다.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>5. 지번 주소의 번지는 숫자 그대로 적습니다. 예) 태평로1가 31, 동인동1가 2-1 (산 번지는 "산 12-3"처럼 "산"을 붙임)</v>
+        <v>4. 도로명주소는 도로명, 지번주소는 법정동(읍·면·동·리) 기준입니다. 행정동 이름(예: 상계1동)은 찾지 못하니 법정동 이름(상계동)으로 적어 주세요.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6. 그 밖의 컬럼(이름, 구분, 직원수 등)은 얼마든지 추가할 수 있고, 모두 지도의 속성으로 저장됩니다. 라벨·팝업에 쓸 컬럼을 나중에 고를 수 있습니다.</v>
+        <v>5. 건물 이름, 층·호수, 괄호는 빼 주세요(번호 뒤는 읽지 않고 버립니다). 예) "세종대로 110 시청 본관 3층" → "세종대로 110"</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>7. 첫 번째 시트의 첫 행이 머리글입니다. 첫 번째 시트만 읽습니다. 이 "작성 안내" 시트는 지워도 됩니다.</v>
+        <v>6. 지번 주소의 번지는 숫자 그대로 적습니다. 예) 태평로1가 31, 동인동1가 2-1 (부번은 "2-1" 또는 "2번지 1호", 산 번지는 "산 12-3"처럼 "산"을 붙임)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>8. 한 번에 올릴 수 있는 행 수는 최대 5,000행입니다.</v>
+        <v>7. 그 밖의 컬럼(이름, 구분, 직원수 등)은 얼마든지 추가할 수 있고, 모두 지도의 속성으로 저장됩니다. 라벨·팝업에 쓸 컬럼을 나중에 고를 수 있습니다.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>9. 찾지 못한 주소는 건너뛰고, 업로드가 끝나면 몇 건이 실패했는지와 행 번호·주소를 알려줍니다.</v>
+        <v>8. 첫 번째 시트의 첫 행이 머리글입니다. 첫 번째 시트만 읽습니다. 이 "작성 안내" 시트는 지워도 됩니다.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9. 한 번에 올릴 수 있는 행 수는 최대 5,000행입니다.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>10. 찾지 못한 주소는 건너뛰고, 업로드가 끝나면 몇 건이 실패했는지와 행 번호·주소·사유(후보)를 알려줍니다.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A14"/>
   </ignoredErrors>
 </worksheet>
 </file>